--- a/태화라이온스 일정표.xlsx
+++ b/태화라이온스 일정표.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\내 드라이브\이재원\클로드코딩\태화라이온스\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{058E8F6C-2726-476C-AFB1-32784F78C164}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8069B75-9DD7-4B6B-BDC7-CE6A935850E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D62689F4-2AA1-4569-97C2-BBDC7B55D2A1}"/>
   </bookViews>
@@ -42,26 +42,14 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>산악회 발대식</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">8일 </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>골프회 정기라운딩</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">11일 </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>보은라이온스클럽 이·취임식</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">14일 </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -81,7 +69,23 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>본회 월례회 및 정기총회, 도산급식 봉사활동</t>
+    <t>산악회 
+발대식</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>골프회
+정기라운딩</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>보은라이온스클럽 
+이·취임식</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>본회 월례회 및 정기총회, 
+도산급식 봉사활동</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -143,12 +147,15 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -492,49 +499,49 @@
   <sheetData>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="33" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="33" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B4" s="2" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
+    <row r="5" spans="1:2" ht="33" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>5</v>
+      <c r="B5" s="2" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" ht="33" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>11</v>
       </c>
     </row>

--- a/태화라이온스 일정표.xlsx
+++ b/태화라이온스 일정표.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\내 드라이브\이재원\클로드코딩\태화라이온스\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8069B75-9DD7-4B6B-BDC7-CE6A935850E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49F89D95-BF94-47FE-8494-2F1918A692D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D62689F4-2AA1-4569-97C2-BBDC7B55D2A1}"/>
+    <workbookView xWindow="-41595" yWindow="-2145" windowWidth="28575" windowHeight="11895" xr2:uid="{D62689F4-2AA1-4569-97C2-BBDC7B55D2A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="22">
   <si>
     <t>5일</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -86,6 +86,46 @@
   <si>
     <t>본회 월례회 및 정기총회, 
 도산급식 봉사활동</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8월</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>14일</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이사회</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">12일 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">15일 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>부부합동월례회</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>월례회</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">28일 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>도산급식 봉사활동</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>골프회 정기라운딩</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -147,7 +187,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -156,6 +196,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -491,7 +534,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21159285-A4BD-44FD-9E4A-15FD187A27CD}">
-  <dimension ref="A2:B7"/>
+  <dimension ref="A2:B14"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="40.25" customWidth="1"/>
@@ -545,6 +588,54 @@
         <v>11</v>
       </c>
     </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/태화라이온스 일정표.xlsx
+++ b/태화라이온스 일정표.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\내 드라이브\이재원\클로드코딩\태화라이온스\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49F89D95-BF94-47FE-8494-2F1918A692D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7659BC77-FD3A-4755-B7E1-BB0E71C7B065}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-41595" yWindow="-2145" windowWidth="28575" windowHeight="11895" xr2:uid="{D62689F4-2AA1-4569-97C2-BBDC7B55D2A1}"/>
+    <workbookView xWindow="-51720" yWindow="-5475" windowWidth="51840" windowHeight="21120" xr2:uid="{D62689F4-2AA1-4569-97C2-BBDC7B55D2A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
   <si>
     <t>5일</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -110,10 +110,6 @@
   </si>
   <si>
     <t>부부합동월례회</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>월례회</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -187,7 +183,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -196,9 +192,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -534,7 +527,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21159285-A4BD-44FD-9E4A-15FD187A27CD}">
-  <dimension ref="A2:B14"/>
+  <dimension ref="A2:B13"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="40.25" customWidth="1"/>
@@ -597,43 +590,35 @@
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>21</v>
+      <c r="B10" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="1" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="1" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B13" s="3" t="s">
+      <c r="A13" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" s="3" t="s">
+      <c r="B13" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/태화라이온스 일정표.xlsx
+++ b/태화라이온스 일정표.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\내 드라이브\이재원\클로드코딩\태화라이온스\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7659BC77-FD3A-4755-B7E1-BB0E71C7B065}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4E6B827-CF66-4BFE-ADD0-230F887353EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-51720" yWindow="-5475" windowWidth="51840" windowHeight="21120" xr2:uid="{D62689F4-2AA1-4569-97C2-BBDC7B55D2A1}"/>
   </bookViews>
@@ -109,10 +109,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>부부합동월례회</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">28일 </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -122,6 +118,10 @@
   </si>
   <si>
     <t>골프회 정기라운딩</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>부부합동 연수회 및 월례회</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -594,7 +594,7 @@
         <v>15</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
@@ -610,15 +610,15 @@
         <v>16</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/태화라이온스 일정표.xlsx
+++ b/태화라이온스 일정표.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\내 드라이브\이재원\클로드코딩\태화라이온스\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4E6B827-CF66-4BFE-ADD0-230F887353EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD4D639A-95B4-497A-ABFC-14FB3B3656BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-51720" yWindow="-5475" windowWidth="51840" windowHeight="21120" xr2:uid="{D62689F4-2AA1-4569-97C2-BBDC7B55D2A1}"/>
+    <workbookView xWindow="-51705" yWindow="-5355" windowWidth="26010" windowHeight="20985" xr2:uid="{D62689F4-2AA1-4569-97C2-BBDC7B55D2A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="25">
   <si>
     <t>5일</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -122,6 +122,22 @@
   </si>
   <si>
     <t>부부합동 연수회 및 월례회</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9월</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">9일 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">미정 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">월례회 </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -527,7 +543,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21159285-A4BD-44FD-9E4A-15FD187A27CD}">
-  <dimension ref="A2:B13"/>
+  <dimension ref="A2:B19"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="40.25" customWidth="1"/>
@@ -621,6 +637,46 @@
         <v>18</v>
       </c>
     </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/태화라이온스 일정표.xlsx
+++ b/태화라이온스 일정표.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\내 드라이브\이재원\클로드코딩\태화라이온스\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD4D639A-95B4-497A-ABFC-14FB3B3656BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{778FC6FC-9F1B-4B7E-98D1-488BD8924DB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-51705" yWindow="-5355" windowWidth="26010" windowHeight="20985" xr2:uid="{D62689F4-2AA1-4569-97C2-BBDC7B55D2A1}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="27">
   <si>
     <t>5일</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -138,6 +138,14 @@
   </si>
   <si>
     <t xml:space="preserve">월례회 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11일</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1부회장 및 신입회원 연수회</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -543,7 +551,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21159285-A4BD-44FD-9E4A-15FD187A27CD}">
-  <dimension ref="A2:B19"/>
+  <dimension ref="A2:B20"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="40.25" customWidth="1"/>
@@ -655,18 +663,18 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
@@ -674,6 +682,14 @@
         <v>23</v>
       </c>
       <c r="B19" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>18</v>
       </c>
     </row>

--- a/태화라이온스 일정표.xlsx
+++ b/태화라이온스 일정표.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\내 드라이브\이재원\클로드코딩\태화라이온스\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{778FC6FC-9F1B-4B7E-98D1-488BD8924DB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFBFBF3E-7882-4473-9729-669D417EB53C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-51705" yWindow="-5355" windowWidth="26010" windowHeight="20985" xr2:uid="{D62689F4-2AA1-4569-97C2-BBDC7B55D2A1}"/>
+    <workbookView xWindow="885" yWindow="2355" windowWidth="21600" windowHeight="11295" xr2:uid="{D62689F4-2AA1-4569-97C2-BBDC7B55D2A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="27">
   <si>
     <t>5일</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -551,7 +551,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21159285-A4BD-44FD-9E4A-15FD187A27CD}">
-  <dimension ref="A2:B20"/>
+  <dimension ref="A2:B19"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="40.25" customWidth="1"/>
@@ -685,14 +685,6 @@
         <v>24</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
